--- a/tools/importer/reports/import-programme-landing.report.xlsx
+++ b/tools/importer/reports/import-programme-landing.report.xlsx
@@ -52,7 +52,7 @@
     <t>content-page</t>
   </si>
   <si>
-    <t>2026-07-24T02:02:32.505Z</t>
+    <t>2026-07-24T02:29:13.986Z</t>
   </si>
   <si>
     <t>Save Our Iconic Kiwi: Our work</t>
@@ -73,7 +73,7 @@
     <t>programme-landing</t>
   </si>
   <si>
-    <t>2026-07-24T02:02:43.979Z</t>
+    <t>2026-07-24T02:29:21.151Z</t>
   </si>
   <si>
     <t>Takahē Recovery Programme</t>
@@ -88,7 +88,7 @@
     <t>get-involved/apply-for-permits/how-we-regulate</t>
   </si>
   <si>
-    <t>2026-07-24T02:02:25.301Z</t>
+    <t>2026-07-24T02:29:06.173Z</t>
   </si>
   <si>
     <t>How we regulate: Permissions</t>
